--- a/Textformating_tasks.xlsx
+++ b/Textformating_tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5BA9F4B5E1762809/Desktop/DATA ANALYSIS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{79DE3D2B-B44B-4BB8-B795-08A903AD6609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1955DF1-75D6-4192-A7C8-7A4DAB4FA50B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D68A6E01-1C75-4D7C-9534-216A04BCA344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{16A12AD7-D809-460D-924B-A436078971F2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="598" xr2:uid="{16A12AD7-D809-460D-924B-A436078971F2}"/>
   </bookViews>
   <sheets>
     <sheet name="DATASET" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="153">
   <si>
     <t>Customer ID</t>
   </si>
@@ -462,50 +462,68 @@
     <t>snehA MENON</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>ṭnk</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
     <t>Column1</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   </t>
+    <t>text join</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>find</t>
   </si>
   <si>
     <t>Column2</t>
   </si>
   <si>
-    <t>CUSTOMER CONCAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,6 +562,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -683,10 +709,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -748,17 +775,52 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="37">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1017,15 +1079,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1098,24 +1151,7 @@
         <name val="Arial Unicode MS"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Unicode MS"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1153,6 +1189,7 @@
         <name val="Arial Unicode MS"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1172,6 +1209,43 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1275,53 +1349,69 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B179FC51-84B1-4676-8A58-8999D6A17D97}" name="Table1" displayName="Table1" ref="A1:S11" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="A1:S11" xr:uid="{B179FC51-84B1-4676-8A58-8999D6A17D97}"/>
-  <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{ADB6CF63-6A4F-4C44-B336-994BCD91B799}" name="Customer ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{C87E634D-6E0E-4207-A548-624DC499CDAD}" name="Raw Customer Name" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{DD5DE457-7966-4995-90B6-E05A652B0B84}" name="1" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B179FC51-84B1-4676-8A58-8999D6A17D97}" name="Table1" displayName="Table1" ref="A1:Y11" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A1:Y11" xr:uid="{B179FC51-84B1-4676-8A58-8999D6A17D97}"/>
+  <tableColumns count="25">
+    <tableColumn id="1" xr3:uid="{ADB6CF63-6A4F-4C44-B336-994BCD91B799}" name="Customer ID" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{C87E634D-6E0E-4207-A548-624DC499CDAD}" name="Raw Customer Name" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{1E5D2C6C-6573-49E0-89E5-54AA5FB54056}" name="1" dataDxfId="32">
       <calculatedColumnFormula>LEFT(Table1[[#This Row],[Customer ID]],4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{23CB54C6-6A27-4945-8269-4DCACCF5B247}" name="2" dataDxfId="25">
+    <tableColumn id="8" xr3:uid="{36B7CE90-3265-4E62-8542-65935AEEA35E}" name="2" dataDxfId="31">
       <calculatedColumnFormula>RIGHT(Table1[[#This Row],[Customer ID]],3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{AE9C3A2F-AD64-4067-B031-5FE6DEEC2388}" name="3" dataDxfId="24">
-      <calculatedColumnFormula>MID(Table1[[#This Row],[Product Code]],5,2)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="11" xr3:uid="{BBBB5D98-0606-4C4E-B388-5737E327AF2B}" name="4" dataDxfId="23">
+    <tableColumn id="9" xr3:uid="{4DD9400F-EE5B-49FF-B684-1F8A3D624265}" name="3" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{47E3818E-AFA0-4E5B-85DA-E5A13BE81CFB}" name="4" dataDxfId="29">
       <calculatedColumnFormula>LEN(Table1[[#This Row],[Raw Customer Name]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{274D4C8D-75D9-4125-B0EC-500255D2E78C}" name="5" dataDxfId="22">
+    <tableColumn id="15" xr3:uid="{A787EAF0-A168-4F7F-ABDF-0FA5910D65C8}" name="42" dataDxfId="28">
+      <calculatedColumnFormula>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{1E5DB26E-BB6E-4112-91AD-819ED5F1B207}" name="43" dataDxfId="27">
+      <calculatedColumnFormula>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{E4805EF1-FD23-475F-ACCE-197899D74693}" name="44" dataDxfId="26">
+      <calculatedColumnFormula>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{15DD172A-2A39-4267-A13F-F7191F11771E}" name="5" dataDxfId="25">
       <calculatedColumnFormula>TRIM(Table1[[#This Row],[Raw Customer Name]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C0375668-DF86-437D-A98A-00D40D02D7FA}" name="TRIM" dataDxfId="21">
-      <calculatedColumnFormula>TRIM(Table1[[#This Row],[5]])</calculatedColumnFormula>
+    <tableColumn id="12" xr3:uid="{77BF476A-9417-423B-82B5-94BD0B13FE40}" name="6" dataDxfId="24">
+      <calculatedColumnFormula>UPPER(Table1[[#This Row],[Raw Customer Name]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3B146281-5013-44F6-83E9-A0FCF1E19E56}" name="Column1" dataDxfId="20">
-      <calculatedColumnFormula>LEN(Table1[[#This Row],[TRIM]])</calculatedColumnFormula>
+    <tableColumn id="13" xr3:uid="{F1185326-C7BD-4EA1-BEBD-C3B58CEAF4BA}" name="7" dataDxfId="23">
+      <calculatedColumnFormula>LOWER(Table1[[#This Row],[Raw Customer Name]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E480A754-FA65-47AB-AAD6-378C87D6D9B1}" name="7" dataDxfId="19">
-      <calculatedColumnFormula>UPPER(Table1[[#This Row],[5]])</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="16" xr3:uid="{1C13E624-2742-4B33-81C9-D40AA11B59D8}" name="8" dataDxfId="18">
-      <calculatedColumnFormula>LOWER(Table1[[#This Row],[7]])</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="17" xr3:uid="{733F85EA-8937-4AD4-8C82-A03482AC211D}" name="9" dataDxfId="17">
+    <tableColumn id="14" xr3:uid="{90E6315A-5E59-4883-BB44-3F6321F9BE54}" name="8" dataDxfId="22">
       <calculatedColumnFormula>PROPER(Table1[[#This Row],[Raw Customer Name]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B9A0994C-7E3E-472E-B35F-74C945EAC40F}" name="Email" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{52C0E72A-53CB-43CE-B213-9841D25FE09D}" name="Phone" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{A86D2511-2754-4B1C-B7F0-27FE9224ECDE}" name="CONCAT" dataDxfId="14">
-      <calculatedColumnFormula>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{B9A0994C-7E3E-472E-B35F-74C945EAC40F}" name="Email" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{52C0E72A-53CB-43CE-B213-9841D25FE09D}" name="Phone" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{E3E47A2A-955A-41E1-8CFA-27C564473FB7}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{B2CFE068-0FB7-4609-ACAB-D60C016E0017}" name="Address" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{735D0188-1FEB-467E-84B6-832003499D22}" name="text join" dataDxfId="7">
+      <calculatedColumnFormula>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E3E47A2A-955A-41E1-8CFA-27C564473FB7}" name="Product Code" dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{12884B30-219E-4EE9-B448-2EBDB95D94C2}" name="CUSTOMER CONCAT" dataDxfId="12">
-      <calculatedColumnFormula>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</calculatedColumnFormula>
+    <tableColumn id="20" xr3:uid="{1734BB4A-74E3-434D-ACAE-B5F99F80E1E0}" name="Column1" dataDxfId="6">
+      <calculatedColumnFormula>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{B2CFE068-0FB7-4609-ACAB-D60C016E0017}" name="Address" dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{A7675176-84F5-4580-B83A-B51E6EA9B9F7}" name="Column2" dataDxfId="10">
-      <calculatedColumnFormula>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</calculatedColumnFormula>
+    <tableColumn id="21" xr3:uid="{AE0B4E01-6738-439F-A4F6-E16BE36B0AC0}" name="0" dataDxfId="5">
+      <calculatedColumnFormula>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="22" xr3:uid="{3D037638-53BF-4532-9837-FDAAFA7DA420}" name="find" dataDxfId="4">
+      <calculatedColumnFormula>FIND("@",Table1[[#This Row],[Email]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="23" xr3:uid="{6F22DD26-C4EE-413B-BAC9-4E9071533B67}" name="Column2" dataDxfId="3">
+      <calculatedColumnFormula>FIND("-",Table1[[#This Row],[Product Code]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="24" xr3:uid="{A1D9135F-1198-48C1-932F-1C32C2E549B2}" name="SEARCH" dataDxfId="2">
+      <calculatedColumnFormula>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="25" xr3:uid="{969CA91F-2633-4C5F-A392-0ADE971CF1E6}" name="Column3" dataDxfId="1">
+      <calculatedColumnFormula>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="26" xr3:uid="{4050BA6F-F29C-4AAA-82B7-6A2B71EBB84E}" name="Column4" dataDxfId="0">
+      <calculatedColumnFormula>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1329,15 +1419,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DAFD145B-2971-491E-900B-3A716BB6A0C3}" name="Table2" displayName="Table2" ref="A3:F19" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A3:F19" xr:uid="{DAFD145B-2971-491E-900B-3A716BB6A0C3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DAFD145B-2971-491E-900B-3A716BB6A0C3}" name="Table2" displayName="Table2" ref="A3:F18" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+  <autoFilter ref="A3:F18" xr:uid="{DAFD145B-2971-491E-900B-3A716BB6A0C3}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F60DB3B5-0C46-48B2-B9BF-62C7F5E83D01}" name="S.No." dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{0778AB1F-09DC-45A3-8187-821F7BF39D53}" name="Function" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{726833DB-EDF0-4175-BA26-F8A6666AFC51}" name="Purpose" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{6D4F86B1-071A-4538-BBBA-B3AE14C59FE1}" name="Syntax" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{99AF5B28-89D8-48BC-AAB9-5DE8660FD27A}" name="Example" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{A4CFBCED-D6FF-4C38-ABA5-687679B4A4B5}" name="Result" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F60DB3B5-0C46-48B2-B9BF-62C7F5E83D01}" name="S.No." dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{0778AB1F-09DC-45A3-8187-821F7BF39D53}" name="Function" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{726833DB-EDF0-4175-BA26-F8A6666AFC51}" name="Purpose" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{6D4F86B1-071A-4538-BBBA-B3AE14C59FE1}" name="Syntax" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{99AF5B28-89D8-48BC-AAB9-5DE8660FD27A}" name="Example" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{A4CFBCED-D6FF-4C38-ABA5-687679B4A4B5}" name="Result" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1640,22 +1730,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB182A77-3C52-47C2-A5C3-154535430225}">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="9" width="21.54296875" customWidth="1"/>
-    <col min="10" max="12" width="30.7265625" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="27.26953125" customWidth="1"/>
-    <col min="15" max="15" width="29.54296875" customWidth="1"/>
-    <col min="17" max="17" width="19.453125" customWidth="1"/>
-    <col min="18" max="18" width="8.7265625" customWidth="1"/>
-    <col min="19" max="19" width="12.6328125" customWidth="1"/>
-    <col min="20" max="20" width="8.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21.54296875" customWidth="1"/>
+    <col min="3" max="3" width="30.6328125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="27.36328125" customWidth="1"/>
+    <col min="6" max="6" width="29.54296875" customWidth="1"/>
+    <col min="7" max="7" width="35" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" customWidth="1"/>
+    <col min="9" max="9" width="34.90625" customWidth="1"/>
+    <col min="17" max="17" width="37.6328125" customWidth="1"/>
+    <col min="18" max="19" width="60.453125" customWidth="1"/>
+    <col min="20" max="20" width="38.08984375" customWidth="1"/>
+    <col min="21" max="21" width="22.81640625" customWidth="1"/>
+    <col min="23" max="23" width="17.26953125" customWidth="1"/>
+    <col min="25" max="25" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="31.5" customHeight="1">
+    <row r="1" spans="1:25" ht="31.5" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1663,58 +1758,76 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>138</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>145</v>
+        <v>5</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>5</v>
+        <v>147</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="43.5">
+        <v>146</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="43.5">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1730,63 +1843,87 @@
         <v>001</v>
       </c>
       <c r="E2" s="3" t="str">
-        <f>MID(Table1[[#This Row],[Product Code]],5,2)</f>
-        <v>HP</v>
+        <f>MID(Table1[[#This Row],[Product Code]],5,3)</f>
+        <v>HP-</v>
       </c>
       <c r="F2" s="3">
         <f>LEN(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>11</v>
       </c>
       <c r="G2" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</f>
+        <v>CUST-001 -LAP-HP-001</v>
+      </c>
+      <c r="H2" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
+        <v>john smith |9876543210</v>
+      </c>
+      <c r="I2" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
+        <v>CUST-001-45 Main Street, Kochi</v>
+      </c>
+      <c r="J2" s="3" t="str">
         <f>TRIM(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>john smith</v>
       </c>
-      <c r="H2" s="3" t="str">
-        <f>TRIM(Table1[[#This Row],[5]])</f>
-        <v>john smith</v>
-      </c>
-      <c r="I2" s="3">
-        <f>LEN(Table1[[#This Row],[TRIM]])</f>
-        <v>10</v>
-      </c>
-      <c r="J2" s="3" t="str">
-        <f>UPPER(Table1[[#This Row],[5]])</f>
-        <v>JOHN SMITH</v>
-      </c>
       <c r="K2" s="3" t="str">
-        <f>LOWER(Table1[[#This Row],[7]])</f>
-        <v>john smith</v>
+        <f>UPPER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v xml:space="preserve">JOHN SMITH </v>
       </c>
       <c r="L2" s="3" t="str">
+        <f>LOWER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v xml:space="preserve">john smith </v>
+      </c>
+      <c r="M2" s="3" t="str">
         <f>PROPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v xml:space="preserve">John Smith </v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="2">
+      <c r="O2" s="2">
         <v>9876543210</v>
-      </c>
-      <c r="O2" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</f>
-        <v>CUST-001-LAP-HP-001</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
-        <v>john smith |9876543210</v>
-      </c>
-      <c r="R2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="R2" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>john smith |john.smith@gmail.com|9876543210|45 Main Street, Kochi</v>
+      </c>
       <c r="S2" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
-        <v>CUST-001-45 Main Street, Kochi</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="43.5">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</f>
+        <v>CUST-001|john smith |john.smith@gmail.com|9876543210</v>
+      </c>
+      <c r="T2" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>john smith |john.smith@gmail.com|9876543210|45 Main Street, Kochi</v>
+      </c>
+      <c r="U2" s="2">
+        <f>FIND("@",Table1[[#This Row],[Email]])</f>
+        <v>11</v>
+      </c>
+      <c r="V2" s="23">
+        <f>FIND("-",Table1[[#This Row],[Product Code]])</f>
+        <v>4</v>
+      </c>
+      <c r="W2" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</f>
+        <v>gmail</v>
+      </c>
+      <c r="X2" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</f>
+        <v>non mob</v>
+      </c>
+      <c r="Y2" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</f>
+        <v>kochi customer</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="43.5">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1801,64 +1938,87 @@
         <f>RIGHT(Table1[[#This Row],[Customer ID]],3)</f>
         <v>002</v>
       </c>
-      <c r="E3" s="3" t="str">
-        <f>MID(Table1[[#This Row],[Product Code]],5,3)</f>
-        <v>SAM</v>
+      <c r="E3" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="F3" s="3">
         <f>LEN(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>9</v>
       </c>
       <c r="G3" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</f>
+        <v>CUST-002 -MOB-SAM-002</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
+        <v>Mary joHN|9876512345</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
+        <v>CUST-002-12 Park Road, Calicut</v>
+      </c>
+      <c r="J3" s="3" t="str">
         <f>TRIM(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>Mary joHN</v>
       </c>
-      <c r="H3" s="3" t="str">
-        <f>TRIM(Table1[[#This Row],[5]])</f>
-        <v>Mary joHN</v>
-      </c>
-      <c r="I3" s="3">
-        <f>LEN(Table1[[#This Row],[TRIM]])</f>
-        <v>9</v>
-      </c>
-      <c r="J3" s="3" t="str">
-        <f>UPPER(Table1[[#This Row],[5]])</f>
+      <c r="K3" s="3" t="str">
+        <f>UPPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>MARY JOHN</v>
       </c>
-      <c r="K3" s="3" t="str">
-        <f>LOWER(Table1[[#This Row],[7]])</f>
+      <c r="L3" s="3" t="str">
+        <f>LOWER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>mary john</v>
       </c>
-      <c r="L3" s="3" t="str">
+      <c r="M3" s="3" t="str">
         <f>PROPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>Mary John</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="2">
+      <c r="O3" s="2">
         <v>9876512345</v>
-      </c>
-      <c r="O3" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</f>
-        <v>CUST-002-MOB-SAM-002</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
-        <v>Mary joHN|9876512345</v>
-      </c>
-      <c r="R3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="R3" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]])</f>
+        <v>CUST-002|Mary joHN|mary.john@yahoo.com</v>
+      </c>
       <c r="S3" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
-        <v>CUST-002-12 Park Road, Calicut</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="43.5">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</f>
+        <v>CUST-002|Mary joHN|mary.john@yahoo.com|9876512345</v>
+      </c>
+      <c r="T3" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>Mary joHN|mary.john@yahoo.com|9876512345|12 Park Road, Calicut</v>
+      </c>
+      <c r="U3" s="2">
+        <f>FIND("@",Table1[[#This Row],[Email]])</f>
+        <v>10</v>
+      </c>
+      <c r="V3" s="23">
+        <f>FIND("-",Table1[[#This Row],[Product Code]])</f>
+        <v>4</v>
+      </c>
+      <c r="W3" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</f>
+        <v>other</v>
+      </c>
+      <c r="X3" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</f>
+        <v>mob</v>
+      </c>
+      <c r="Y3" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</f>
+        <v>other location</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="43.5">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -1882,55 +2042,79 @@
         <v>11</v>
       </c>
       <c r="G4" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</f>
+        <v>CUST-003 -TAB-APP-003</v>
+      </c>
+      <c r="H4" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
+        <v>rahul kumar|9847012345</v>
+      </c>
+      <c r="I4" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
+        <v>CUST-003-78 MG Road, Thrissur</v>
+      </c>
+      <c r="J4" s="3" t="str">
         <f>TRIM(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>rahul kumar</v>
       </c>
-      <c r="H4" s="3" t="str">
-        <f>TRIM(Table1[[#This Row],[5]])</f>
+      <c r="K4" s="3" t="str">
+        <f>UPPER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v>RAHUL KUMAR</v>
+      </c>
+      <c r="L4" s="3" t="str">
+        <f>LOWER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>rahul kumar</v>
       </c>
-      <c r="I4" s="3">
-        <f>LEN(Table1[[#This Row],[TRIM]])</f>
-        <v>11</v>
-      </c>
-      <c r="J4" s="3" t="str">
-        <f>UPPER(Table1[[#This Row],[5]])</f>
-        <v>RAHUL KUMAR</v>
-      </c>
-      <c r="K4" s="3" t="str">
-        <f>LOWER(Table1[[#This Row],[7]])</f>
-        <v>rahul kumar</v>
-      </c>
-      <c r="L4" s="3" t="str">
+      <c r="M4" s="3" t="str">
         <f>PROPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>Rahul Kumar</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="2">
+      <c r="O4" s="2">
         <v>9847012345</v>
-      </c>
-      <c r="O4" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</f>
-        <v>CUST-003-TAB-APP-003</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
-        <v>rahul kumar|9847012345</v>
-      </c>
-      <c r="R4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="R4" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]])</f>
+        <v>CUST-003|rahul kumar|rahul.kumar@gmail.com</v>
+      </c>
       <c r="S4" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
-        <v>CUST-003-78 MG Road, Thrissur</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="43.5">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</f>
+        <v>CUST-003|rahul kumar|rahul.kumar@gmail.com|9847012345</v>
+      </c>
+      <c r="T4" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>rahul kumar|rahul.kumar@gmail.com|9847012345|78 MG Road, Thrissur</v>
+      </c>
+      <c r="U4" s="2">
+        <f>FIND("@",Table1[[#This Row],[Email]])</f>
+        <v>12</v>
+      </c>
+      <c r="V4" s="23">
+        <f>FIND("-",Table1[[#This Row],[Product Code]])</f>
+        <v>4</v>
+      </c>
+      <c r="W4" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</f>
+        <v>gmail</v>
+      </c>
+      <c r="X4" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</f>
+        <v>non mob</v>
+      </c>
+      <c r="Y4" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</f>
+        <v>other location</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="43.5">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -1954,55 +2138,79 @@
         <v>12</v>
       </c>
       <c r="G5" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</f>
+        <v>CUST-004 -LAP-DEL-004</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
+        <v>aNJALI nAIR |9988776655</v>
+      </c>
+      <c r="I5" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
+        <v>CUST-004-23 Lake View, Kochi</v>
+      </c>
+      <c r="J5" s="3" t="str">
         <f>TRIM(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>aNJALI nAIR</v>
       </c>
-      <c r="H5" s="3" t="str">
-        <f>TRIM(Table1[[#This Row],[5]])</f>
-        <v>aNJALI nAIR</v>
-      </c>
-      <c r="I5" s="3">
-        <f>LEN(Table1[[#This Row],[TRIM]])</f>
-        <v>11</v>
-      </c>
-      <c r="J5" s="3" t="str">
-        <f>UPPER(Table1[[#This Row],[5]])</f>
-        <v>ANJALI NAIR</v>
-      </c>
       <c r="K5" s="3" t="str">
-        <f>LOWER(Table1[[#This Row],[7]])</f>
-        <v>anjali nair</v>
+        <f>UPPER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v xml:space="preserve">ANJALI NAIR </v>
       </c>
       <c r="L5" s="3" t="str">
+        <f>LOWER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v xml:space="preserve">anjali nair </v>
+      </c>
+      <c r="M5" s="3" t="str">
         <f>PROPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v xml:space="preserve">Anjali Nair </v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="2">
+      <c r="O5" s="2">
         <v>9988776655</v>
-      </c>
-      <c r="O5" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</f>
-        <v>CUST-004-LAP-DEL-004</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q5" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
-        <v>aNJALI nAIR |9988776655</v>
-      </c>
-      <c r="R5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="R5" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]])</f>
+        <v>CUST-004|aNJALI nAIR |anjali.nair@outlook.com</v>
+      </c>
       <c r="S5" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
-        <v>CUST-004-23 Lake View, Kochi</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="58">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</f>
+        <v>CUST-004|aNJALI nAIR |anjali.nair@outlook.com|9988776655</v>
+      </c>
+      <c r="T5" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>aNJALI nAIR |anjali.nair@outlook.com|9988776655|23 Lake View, Kochi</v>
+      </c>
+      <c r="U5" s="2">
+        <f>FIND("@",Table1[[#This Row],[Email]])</f>
+        <v>12</v>
+      </c>
+      <c r="V5" s="23">
+        <f>FIND("-",Table1[[#This Row],[Product Code]])</f>
+        <v>4</v>
+      </c>
+      <c r="W5" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</f>
+        <v>other</v>
+      </c>
+      <c r="X5" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</f>
+        <v>non mob</v>
+      </c>
+      <c r="Y5" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</f>
+        <v>kochi customer</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="43.5">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -2026,55 +2234,79 @@
         <v>10</v>
       </c>
       <c r="G6" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</f>
+        <v>CUST-005 -MOB-ONE-005</v>
+      </c>
+      <c r="H6" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
+        <v>ahmed ali |9876123456</v>
+      </c>
+      <c r="I6" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
+        <v>CUST-005-89 Market Road, Kannur</v>
+      </c>
+      <c r="J6" s="3" t="str">
         <f>TRIM(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>ahmed ali</v>
       </c>
-      <c r="H6" s="3" t="str">
-        <f>TRIM(Table1[[#This Row],[5]])</f>
-        <v>ahmed ali</v>
-      </c>
-      <c r="I6" s="3">
-        <f>LEN(Table1[[#This Row],[TRIM]])</f>
-        <v>9</v>
-      </c>
-      <c r="J6" s="3" t="str">
-        <f>UPPER(Table1[[#This Row],[5]])</f>
-        <v>AHMED ALI</v>
-      </c>
       <c r="K6" s="3" t="str">
-        <f>LOWER(Table1[[#This Row],[7]])</f>
-        <v>ahmed ali</v>
+        <f>UPPER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v xml:space="preserve">AHMED ALI </v>
       </c>
       <c r="L6" s="3" t="str">
+        <f>LOWER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v xml:space="preserve">ahmed ali </v>
+      </c>
+      <c r="M6" s="3" t="str">
         <f>PROPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v xml:space="preserve">Ahmed Ali </v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="2">
+      <c r="O6" s="2">
         <v>9876123456</v>
-      </c>
-      <c r="O6" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</f>
-        <v>CUST-005-MOB-ONE-005</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q6" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
-        <v>ahmed ali |9876123456</v>
-      </c>
-      <c r="R6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="R6" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]])</f>
+        <v>CUST-005|ahmed ali |ahmed.ali@gmail.com</v>
+      </c>
       <c r="S6" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
-        <v>CUST-005-89 Market Road, Kannur</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="58">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</f>
+        <v>CUST-005|ahmed ali |ahmed.ali@gmail.com|9876123456</v>
+      </c>
+      <c r="T6" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>ahmed ali |ahmed.ali@gmail.com|9876123456|89 Market Road, Kannur</v>
+      </c>
+      <c r="U6" s="2">
+        <f>FIND("@",Table1[[#This Row],[Email]])</f>
+        <v>10</v>
+      </c>
+      <c r="V6" s="23">
+        <f>FIND("-",Table1[[#This Row],[Product Code]])</f>
+        <v>4</v>
+      </c>
+      <c r="W6" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</f>
+        <v>gmail</v>
+      </c>
+      <c r="X6" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</f>
+        <v>mob</v>
+      </c>
+      <c r="Y6" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</f>
+        <v>other location</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="58">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -2098,55 +2330,79 @@
         <v>11</v>
       </c>
       <c r="G7" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</f>
+        <v>CUST-006 -LAP-LEN-006</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
+        <v>snehA MENON|9847123456</v>
+      </c>
+      <c r="I7" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
+        <v>CUST-006-34 Station Road, Aluva</v>
+      </c>
+      <c r="J7" s="3" t="str">
         <f>TRIM(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>snehA MENON</v>
       </c>
-      <c r="H7" s="3" t="str">
-        <f>TRIM(Table1[[#This Row],[5]])</f>
-        <v>snehA MENON</v>
-      </c>
-      <c r="I7" s="3">
-        <f>LEN(Table1[[#This Row],[TRIM]])</f>
-        <v>11</v>
-      </c>
-      <c r="J7" s="3" t="str">
-        <f>UPPER(Table1[[#This Row],[5]])</f>
+      <c r="K7" s="3" t="str">
+        <f>UPPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>SNEHA MENON</v>
       </c>
-      <c r="K7" s="3" t="str">
-        <f>LOWER(Table1[[#This Row],[7]])</f>
+      <c r="L7" s="3" t="str">
+        <f>LOWER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>sneha menon</v>
       </c>
-      <c r="L7" s="3" t="str">
+      <c r="M7" s="3" t="str">
         <f>PROPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>Sneha Menon</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>9847123456</v>
-      </c>
-      <c r="O7" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</f>
-        <v>CUST-006-LAP-LEN-006</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q7" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
-        <v>snehA MENON|9847123456</v>
-      </c>
-      <c r="R7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="R7" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]])</f>
+        <v>CUST-006|snehA MENON|sneha.menon@yahoo.com</v>
+      </c>
       <c r="S7" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
-        <v>CUST-006-34 Station Road, Aluva</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="58">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</f>
+        <v>CUST-006|snehA MENON|sneha.menon@yahoo.com|9847123456</v>
+      </c>
+      <c r="T7" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>snehA MENON|sneha.menon@yahoo.com|9847123456|34 Station Road, Aluva</v>
+      </c>
+      <c r="U7" s="2">
+        <f>FIND("@",Table1[[#This Row],[Email]])</f>
+        <v>12</v>
+      </c>
+      <c r="V7" s="23">
+        <f>FIND("-",Table1[[#This Row],[Product Code]])</f>
+        <v>4</v>
+      </c>
+      <c r="W7" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</f>
+        <v>other</v>
+      </c>
+      <c r="X7" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</f>
+        <v>non mob</v>
+      </c>
+      <c r="Y7" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</f>
+        <v>other location</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="43.5">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -2170,58 +2426,79 @@
         <v>9</v>
       </c>
       <c r="G8" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</f>
+        <v>CUST-007 -TAB-SAM-007</v>
+      </c>
+      <c r="H8" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
+        <v>arjun das|9966123456</v>
+      </c>
+      <c r="I8" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
+        <v>CUST-007-56 Beach Road, Kozhikode</v>
+      </c>
+      <c r="J8" s="3" t="str">
         <f>TRIM(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>arjun das</v>
       </c>
-      <c r="H8" s="3" t="str">
-        <f>TRIM(Table1[[#This Row],[5]])</f>
+      <c r="K8" s="3" t="str">
+        <f>UPPER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v>ARJUN DAS</v>
+      </c>
+      <c r="L8" s="3" t="str">
+        <f>LOWER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>arjun das</v>
       </c>
-      <c r="I8" s="3">
-        <f>LEN(Table1[[#This Row],[TRIM]])</f>
-        <v>9</v>
-      </c>
-      <c r="J8" s="3" t="str">
-        <f>UPPER(Table1[[#This Row],[5]])</f>
-        <v>ARJUN DAS</v>
-      </c>
-      <c r="K8" s="3" t="str">
-        <f>LOWER(Table1[[#This Row],[7]])</f>
-        <v>arjun das</v>
-      </c>
-      <c r="L8" s="3" t="str">
+      <c r="M8" s="3" t="str">
         <f>PROPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>Arjun Das</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="N8" s="2">
+      <c r="O8" s="2">
         <v>9966123456</v>
-      </c>
-      <c r="O8" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</f>
-        <v>CUST-007-TAB-SAM-007</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q8" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
-        <v>arjun das|9966123456</v>
-      </c>
-      <c r="R8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="R8" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]])</f>
+        <v>CUST-007|arjun das|arjun.das@gmail.com</v>
+      </c>
       <c r="S8" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
-        <v>CUST-007-56 Beach Road, Kozhikode</v>
-      </c>
-      <c r="T8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="72.5">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</f>
+        <v>CUST-007|arjun das|arjun.das@gmail.com|9966123456</v>
+      </c>
+      <c r="T8" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>arjun das|arjun.das@gmail.com|9966123456|56 Beach Road, Kozhikode</v>
+      </c>
+      <c r="U8" s="2">
+        <f>FIND("@",Table1[[#This Row],[Email]])</f>
+        <v>10</v>
+      </c>
+      <c r="V8" s="23">
+        <f>FIND("-",Table1[[#This Row],[Product Code]])</f>
+        <v>4</v>
+      </c>
+      <c r="W8" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</f>
+        <v>gmail</v>
+      </c>
+      <c r="X8" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</f>
+        <v>non mob</v>
+      </c>
+      <c r="Y8" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</f>
+        <v>other location</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="43.5">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -2245,55 +2522,79 @@
         <v>13</v>
       </c>
       <c r="G9" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</f>
+        <v>CUST-008 -MOB-RED-008</v>
+      </c>
+      <c r="H9" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
+        <v>FATHIMA KHAN |9895123456</v>
+      </c>
+      <c r="I9" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
+        <v>CUST-008-90 College Road, Malappuram</v>
+      </c>
+      <c r="J9" s="3" t="str">
         <f>TRIM(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>FATHIMA KHAN</v>
       </c>
-      <c r="H9" s="3" t="str">
-        <f>TRIM(Table1[[#This Row],[5]])</f>
-        <v>FATHIMA KHAN</v>
-      </c>
-      <c r="I9" s="3">
-        <f>LEN(Table1[[#This Row],[TRIM]])</f>
-        <v>12</v>
-      </c>
-      <c r="J9" s="3" t="str">
-        <f>UPPER(Table1[[#This Row],[5]])</f>
-        <v>FATHIMA KHAN</v>
-      </c>
       <c r="K9" s="3" t="str">
-        <f>LOWER(Table1[[#This Row],[7]])</f>
-        <v>fathima khan</v>
+        <f>UPPER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v xml:space="preserve">FATHIMA KHAN </v>
       </c>
       <c r="L9" s="3" t="str">
+        <f>LOWER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v xml:space="preserve">fathima khan </v>
+      </c>
+      <c r="M9" s="3" t="str">
         <f>PROPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v xml:space="preserve">Fathima Khan </v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="N9" s="2">
+      <c r="O9" s="2">
         <v>9895123456</v>
-      </c>
-      <c r="O9" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</f>
-        <v>CUST-008-MOB-RED-008</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q9" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
-        <v>FATHIMA KHAN |9895123456</v>
-      </c>
-      <c r="R9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="R9" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]])</f>
+        <v>CUST-008|FATHIMA KHAN |fathima.khan@outlook.com</v>
+      </c>
       <c r="S9" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
-        <v>CUST-008-90 College Road, Malappuram</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="58">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</f>
+        <v>CUST-008|FATHIMA KHAN |fathima.khan@outlook.com|9895123456</v>
+      </c>
+      <c r="T9" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>FATHIMA KHAN |fathima.khan@outlook.com|9895123456|90 College Road, Malappuram</v>
+      </c>
+      <c r="U9" s="2">
+        <f>FIND("@",Table1[[#This Row],[Email]])</f>
+        <v>13</v>
+      </c>
+      <c r="V9" s="23">
+        <f>FIND("-",Table1[[#This Row],[Product Code]])</f>
+        <v>4</v>
+      </c>
+      <c r="W9" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</f>
+        <v>other</v>
+      </c>
+      <c r="X9" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</f>
+        <v>mob</v>
+      </c>
+      <c r="Y9" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</f>
+        <v>other location</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="43.5">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -2317,55 +2618,79 @@
         <v>11</v>
       </c>
       <c r="G10" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</f>
+        <v>CUST-009 -LAP-ASU-009</v>
+      </c>
+      <c r="H10" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
+        <v>vishnu raj |9746123456</v>
+      </c>
+      <c r="I10" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
+        <v>CUST-009-11 Temple Road, Kottayam</v>
+      </c>
+      <c r="J10" s="3" t="str">
         <f>TRIM(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>vishnu raj</v>
       </c>
-      <c r="H10" s="3" t="str">
-        <f>TRIM(Table1[[#This Row],[5]])</f>
-        <v>vishnu raj</v>
-      </c>
-      <c r="I10" s="3">
-        <f>LEN(Table1[[#This Row],[TRIM]])</f>
-        <v>10</v>
-      </c>
-      <c r="J10" s="3" t="str">
-        <f>UPPER(Table1[[#This Row],[5]])</f>
-        <v>VISHNU RAJ</v>
-      </c>
       <c r="K10" s="3" t="str">
-        <f>LOWER(Table1[[#This Row],[7]])</f>
-        <v>vishnu raj</v>
+        <f>UPPER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v xml:space="preserve">VISHNU RAJ </v>
       </c>
       <c r="L10" s="3" t="str">
+        <f>LOWER(Table1[[#This Row],[Raw Customer Name]])</f>
+        <v xml:space="preserve">vishnu raj </v>
+      </c>
+      <c r="M10" s="3" t="str">
         <f>PROPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v xml:space="preserve">Vishnu Raj </v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N10" s="2">
+      <c r="O10" s="2">
         <v>9746123456</v>
-      </c>
-      <c r="O10" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</f>
-        <v>CUST-009-LAP-ASU-009</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Q10" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
-        <v>vishnu raj |9746123456</v>
-      </c>
-      <c r="R10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="R10" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]])</f>
+        <v>CUST-009|vishnu raj |vishnu.raj@gmail.com</v>
+      </c>
       <c r="S10" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
-        <v>CUST-009-11 Temple Road, Kottayam</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="58">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</f>
+        <v>CUST-009|vishnu raj |vishnu.raj@gmail.com|9746123456</v>
+      </c>
+      <c r="T10" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>vishnu raj |vishnu.raj@gmail.com|9746123456|11 Temple Road, Kottayam</v>
+      </c>
+      <c r="U10" s="2">
+        <f>FIND("@",Table1[[#This Row],[Email]])</f>
+        <v>11</v>
+      </c>
+      <c r="V10" s="23">
+        <f>FIND("-",Table1[[#This Row],[Product Code]])</f>
+        <v>4</v>
+      </c>
+      <c r="W10" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</f>
+        <v>gmail</v>
+      </c>
+      <c r="X10" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</f>
+        <v>non mob</v>
+      </c>
+      <c r="Y10" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</f>
+        <v>other location</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="43.5">
       <c r="A11" s="2" t="s">
         <v>48</v>
       </c>
@@ -2389,62 +2714,86 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]]," -",Table1[[#This Row],[Product Code]])</f>
+        <v>CUST-010 -MOB-VIV-010</v>
+      </c>
+      <c r="H11" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
+        <v>PRIYA SHARMA|9846123456</v>
+      </c>
+      <c r="I11" s="3" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
+        <v>CUST-010-67 Hill Road, Ernakulam</v>
+      </c>
+      <c r="J11" s="3" t="str">
         <f>TRIM(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>PRIYA SHARMA</v>
       </c>
-      <c r="H11" s="3" t="str">
-        <f>TRIM(Table1[[#This Row],[5]])</f>
+      <c r="K11" s="3" t="str">
+        <f>UPPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>PRIYA SHARMA</v>
       </c>
-      <c r="I11" s="3">
-        <f>LEN(Table1[[#This Row],[TRIM]])</f>
-        <v>12</v>
-      </c>
-      <c r="J11" s="3" t="str">
-        <f>UPPER(Table1[[#This Row],[5]])</f>
-        <v>PRIYA SHARMA</v>
-      </c>
-      <c r="K11" s="3" t="str">
-        <f>LOWER(Table1[[#This Row],[7]])</f>
+      <c r="L11" s="3" t="str">
+        <f>LOWER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>priya sharma</v>
       </c>
-      <c r="L11" s="3" t="str">
+      <c r="M11" s="3" t="str">
         <f>PROPER(Table1[[#This Row],[Raw Customer Name]])</f>
         <v>Priya Sharma</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="2">
+      <c r="O11" s="2">
         <v>9846123456</v>
-      </c>
-      <c r="O11" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Product Code]])</f>
-        <v>CUST-010-MOB-VIV-010</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q11" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Raw Customer Name]],"|",Table1[[#This Row],[Phone]])</f>
-        <v>PRIYA SHARMA|9846123456</v>
-      </c>
-      <c r="R11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="R11" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]])</f>
+        <v>CUST-010|PRIYA SHARMA|priya.sharma@yahoo.com</v>
+      </c>
       <c r="S11" s="2" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Customer ID]],"-",Table1[[#This Row],[Address]])</f>
-        <v>CUST-010-67 Hill Road, Ernakulam</v>
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Customer ID]],Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]])</f>
+        <v>CUST-010|PRIYA SHARMA|priya.sharma@yahoo.com|9846123456</v>
+      </c>
+      <c r="T11" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,Table1[[#This Row],[Raw Customer Name]],Table1[[#This Row],[Email]],Table1[[#This Row],[Phone]],Table1[[#This Row],[Address]])</f>
+        <v>PRIYA SHARMA|priya.sharma@yahoo.com|9846123456|67 Hill Road, Ernakulam</v>
+      </c>
+      <c r="U11" s="2">
+        <f>FIND("@",Table1[[#This Row],[Email]])</f>
+        <v>13</v>
+      </c>
+      <c r="V11" s="23">
+        <f>FIND("-",Table1[[#This Row],[Product Code]])</f>
+        <v>4</v>
+      </c>
+      <c r="W11" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("gmail",Table1[[#This Row],[Email]])),"gmail","other")</f>
+        <v>other</v>
+      </c>
+      <c r="X11" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("mob",Table1[[#This Row],[Product Code]])),"mob","non mob")</f>
+        <v>mob</v>
+      </c>
+      <c r="Y11" s="23" t="str">
+        <f>IF(ISNUMBER(SEARCH("kochi",Table1[[#This Row],[Address]])),"kochi customer","other location")</f>
+        <v>other location</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{7269ECE1-E957-49FB-877B-2253695A4651}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="E3:E6" calculatedColumn="1"/>
-  </ignoredErrors>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2454,11 +2803,11 @@
   <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="17.26953125" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" customWidth="1"/>
     <col min="3" max="3" width="40.54296875" customWidth="1"/>
-    <col min="4" max="4" width="35.81640625" customWidth="1"/>
-    <col min="5" max="5" width="46.1796875" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" customWidth="1"/>
+    <col min="4" max="4" width="35.90625" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" customWidth="1"/>
+    <col min="6" max="6" width="20.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.5">
@@ -2791,16 +3140,6 @@
       <c r="F18" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="21"/>
     </row>
     <row r="20" spans="1:6" ht="17.5">
       <c r="A20" s="6"/>
